--- a/docs/就職活動メモシステム.テスト仕様書.xlsx
+++ b/docs/就職活動メモシステム.テスト仕様書.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2784,6 +2784,51 @@
       <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>確認後は型を「文字列型」に戻すこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>メモ一覧／メモ編集</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>表示確認</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>日付型の表示とカレンダー入力</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>項目設定で対象項目（例：項目16「締切日」）の型を「日付型」に変更して保存し、メモ一覧と編集画面を確認する</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>一覧では保存値（数字のみ yyyyMMdd）が yyyy/mm/dd 形式（例：20261031 → 2026/10/31）で表示されること。編集画面ではカレンダーで入力でき、保存すると memo_records の該当項目に数字のみ（yyyyMMdd）で保存されること</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>確認後は型を「文字列型」に戻すこと</t>
         </is>
